--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22065" windowHeight="9810"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（中）" sheetId="1" r:id="rId1"/>
@@ -214,6 +214,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>choice(</t>
     </r>
     <r>
@@ -1011,6 +1016,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -1131,7 +1141,25 @@
     <t>那只飞蛾在楼道的阴影中奋力扑腾着翅膀，仿佛仍不死心地试图挽留你们前进的脚步。但这一次，除了在空气中留下一团淡淡的光点外，它再也没能激起你们半分停留的心思。</t>
   </si>
   <si>
-    <t>loadScript(克拉克线4层（上）_1, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_clark4F(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 1)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=21; gotomainline=克拉克线4层（上）_1</t>
@@ -6459,7 +6487,7 @@
       <c r="J95" t="s">
         <v>15</v>
       </c>
-      <c r="K95" t="s">
+      <c r="K95" s="2" t="s">
         <v>303</v>
       </c>
       <c r="L95" t="s">
